--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/ELAN/ELAN+50T+50EP+optim_purn/params_vs_psnr_analysis/ELAN_hutcn_hyperopt_study_full.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/ELAN/ELAN+50T+50EP+optim_purn/params_vs_psnr_analysis/ELAN_hutcn_hyperopt_study_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,50 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>flops_G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hp_n_feats</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp_num_heads</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hp_num_blocks</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hp_window_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hp_patch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hp_optimizer</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hp_scheduler</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hp_loss</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hp_lr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hp_weight_decay</t>
         </is>
@@ -506,39 +511,42 @@
         <v>27.66504058837891</v>
       </c>
       <c r="D2" t="n">
+        <v>2.124024012</v>
+      </c>
+      <c r="E2" t="n">
         <v>88</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>192</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3.135775732257744e-05</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1.256277350380703e-05</v>
       </c>
     </row>
@@ -553,39 +561,42 @@
         <v>28.0554084777832</v>
       </c>
       <c r="D3" t="n">
+        <v>2.268395712</v>
+      </c>
+      <c r="E3" t="n">
         <v>96</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
         <v>160</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3.385226783451975e-05</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3.632486956676606e-05</v>
       </c>
     </row>
@@ -600,39 +611,42 @@
         <v>28.07649307250977</v>
       </c>
       <c r="D4" t="n">
+        <v>4.067064</v>
+      </c>
+      <c r="E4" t="n">
         <v>96</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>224</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.0002051259942215138</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>3.9459088111e-06</v>
       </c>
     </row>
@@ -647,39 +661,42 @@
         <v>29.84953155517578</v>
       </c>
       <c r="D5" t="n">
+        <v>1.444006656</v>
+      </c>
+      <c r="E5" t="n">
         <v>64</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>128</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.0002041033406525706</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3.02961044282125e-05</v>
       </c>
     </row>
@@ -694,39 +711,42 @@
         <v>30.53452568054199</v>
       </c>
       <c r="D6" t="n">
+        <v>3.836590272</v>
+      </c>
+      <c r="E6" t="n">
         <v>96</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>192</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.0003284210350911732</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>4.149795789891592e-05</v>
       </c>
     </row>
@@ -741,39 +761,42 @@
         <v>28.18730812072754</v>
       </c>
       <c r="D7" t="n">
+        <v>4.95144414</v>
+      </c>
+      <c r="E7" t="n">
         <v>120</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>8</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>128</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>6.995363653959081e-05</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>7.991621920384356e-06</v>
       </c>
     </row>
@@ -788,39 +811,42 @@
         <v>27.87917518615723</v>
       </c>
       <c r="D8" t="n">
+        <v>1.59994296</v>
+      </c>
+      <c r="E8" t="n">
         <v>80</v>
       </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>160</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>3.50748407899447e-05</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>3.627066608804412e-06</v>
       </c>
     </row>
@@ -835,39 +861,42 @@
         <v>27.95033226013184</v>
       </c>
       <c r="D9" t="n">
+        <v>1.444006656</v>
+      </c>
+      <c r="E9" t="n">
         <v>64</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>160</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1.43939108932709e-05</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.0004916400722913762</v>
       </c>
     </row>
@@ -882,39 +911,42 @@
         <v>29.32700309753418</v>
       </c>
       <c r="D10" t="n">
+        <v>1.357007616</v>
+      </c>
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
       <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
         <v>224</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>4.654373626005679e-05</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.0004743945221058974</v>
       </c>
     </row>
@@ -929,39 +961,42 @@
         <v>30.03757743835449</v>
       </c>
       <c r="D11" t="n">
+        <v>2.81829816</v>
+      </c>
+      <c r="E11" t="n">
         <v>80</v>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>128</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.0004802670023396567</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>5.595888766717815e-05</v>
       </c>
     </row>
@@ -976,39 +1011,42 @@
         <v>30.30857734680176</v>
       </c>
       <c r="D12" t="n">
+        <v>2.81829816</v>
+      </c>
+      <c r="E12" t="n">
         <v>80</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
       <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>12</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>128</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.0004225203727275751</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.0001131681277037403</v>
       </c>
     </row>
@@ -1023,39 +1061,42 @@
         <v>30.3171802520752</v>
       </c>
       <c r="D13" t="n">
+        <v>3.308501196</v>
+      </c>
+      <c r="E13" t="n">
         <v>88</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>12</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>192</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.000194177623652542</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.0001829157263322556</v>
       </c>
     </row>
@@ -1070,39 +1111,42 @@
         <v>30.43386116027832</v>
       </c>
       <c r="D14" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="E14" t="n">
         <v>72</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>192</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.0002989269311703188</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1.52147208676072e-06</v>
       </c>
     </row>
@@ -1117,39 +1161,42 @@
         <v>30.35392265319824</v>
       </c>
       <c r="D15" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="E15" t="n">
         <v>72</v>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
         <v>12</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>192</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.0003287372398316848</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6.212848969801366e-05</v>
       </c>
     </row>
@@ -1164,39 +1211,42 @@
         <v>30.37254409790039</v>
       </c>
       <c r="D16" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="E16" t="n">
         <v>72</v>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
         <v>12</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>192</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.0002927269457105701</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1.752973172833225e-05</v>
       </c>
     </row>
@@ -1211,39 +1261,42 @@
         <v>30.13906059265137</v>
       </c>
       <c r="D17" t="n">
+        <v>6.26621688</v>
+      </c>
+      <c r="E17" t="n">
         <v>112</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
         <v>12</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>192</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>8.472635160092751e-05</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3.236079391157211e-06</v>
       </c>
     </row>
@@ -1258,39 +1311,42 @@
         <v>30.50540199279785</v>
       </c>
       <c r="D18" t="n">
+        <v>4.15235502</v>
+      </c>
+      <c r="E18" t="n">
         <v>88</v>
       </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
         <v>12</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>192</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.0003244684367854916</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1.971762311203102e-05</v>
       </c>
     </row>
@@ -1305,39 +1361,42 @@
         <v>30.64372634887695</v>
       </c>
       <c r="D19" t="n">
+        <v>4.81024224</v>
+      </c>
+      <c r="E19" t="n">
         <v>96</v>
       </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>192</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.0003647017198842633</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1.905021901044231e-06</v>
       </c>
     </row>
@@ -1352,39 +1411,42 @@
         <v>30.35832939147949</v>
       </c>
       <c r="D20" t="n">
+        <v>3.621157056</v>
+      </c>
+      <c r="E20" t="n">
         <v>96</v>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>4</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
         <v>160</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.000390864261174051</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1.876804016731845e-06</v>
       </c>
     </row>
@@ -1399,39 +1461,42 @@
         <v>30.52601699829102</v>
       </c>
       <c r="D21" t="n">
+        <v>5.006426544</v>
+      </c>
+      <c r="E21" t="n">
         <v>112</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
       <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>12</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>192</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.0002198507792378718</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1.958623019609344e-06</v>
       </c>
     </row>
@@ -1446,39 +1511,42 @@
         <v>30.39954299926758</v>
       </c>
       <c r="D22" t="n">
+        <v>3.308501196</v>
+      </c>
+      <c r="E22" t="n">
         <v>88</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>12</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>192</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.0001966400626179037</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>4.809556523313412e-05</v>
       </c>
     </row>
